--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_013/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_013/extracted.xlsx
@@ -485,6 +485,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -560,6 +565,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -595,6 +615,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -630,11 +655,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -670,6 +690,16 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="I5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -700,17 +730,47 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1343,17 +1403,17 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Cementless Femoral Stem FEA — Rev F Press-Fit Study</t>
+          <t>Cementless Femoral Stem FEA — Rev F Press-Fit</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Predict bone–implant interface micromotion during early gait loading to support acceptance decision for Rev F femoral stem</t>
+          <t>Predict peak bone–implant interface micromotion during early gait loading to support acceptance decision for Rev F femoral stem</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Structural FEA (Abaqus/Standard) of a cementless Ti-6Al-4V femoral stem press-fit into a synthetic femur. The model predicts peak relative micromotion at the medial–lateral proximal interface, stem von Mises stress, and contact pressure distribution under single-leg stance and heel-strike load cases (3.0 kN joint reaction). Results are used to compare Rev F vs Rev D designs, rank broach fits and knurl patterns, and evaluate whether peak micromotion remains below a 40 µm threshold with a &gt;20% safety margin.</t>
+          <t>Structural finite element analysis (Abaqus/Standard) of a cementless Ti-6Al-4V femoral stem press-fitted into a synthetic femur (Sawbones 3403). The context of use is to demonstrate that peak relative micromotion at the medial–lateral proximal interface remains below 40 µm under single-leg stance and heel-strike load cases, and to rank design variants (Rev D vs Rev F, broach sizes S/M/L, knurl patterns) by predicted micromotion. Model outputs include peak micromotion, stem von Mises stress, and contact pressure distribution. Results feed a gate review acceptance decision with a required safety margin &gt; 20% on the 40 µm threshold.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1363,12 +1423,12 @@
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Class III</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
         <is>
-          <t>MRL 4</t>
+          <t>MRL 3</t>
         </is>
       </c>
       <c r="G3" s="39" t="inlineStr">
@@ -1387,9 +1447,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -1985,7 +2045,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Bone–Implant Interface Micromotion Threshold</t>
+          <t>Micromotion Threshold Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -1995,7 +2055,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Peak relative micromotion at the proximal medial–lateral interface must remain below 40 µm during early gait loading, with a safety margin &gt;20% relative to threshold, to support Rev F acceptance.</t>
+          <t>Peak relative micromotion at the medial–lateral proximal bone–implant interface must remain below 40 µm during single-leg stance and heel-strike loading, with a safety margin greater than 20% relative to that threshold, for Rev F stem acceptance at gate review.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2017,13 +2077,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Abaqus/Standard Structural FEA Model — Femoral Stem Press-Fit</t>
+          <t>Abaqus/Standard Structural FEA Model — Rev F Femoral Stem</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Nonlinear static FEA model of CT-derived femur (DigitalFemur-42) with Rev F Ti-6Al-4V stem, surface-to-surface frictional contact (μ=0.30), bilinear plastic stem material, and porous layer stiffness grading via USDFLD subroutine; run in Abaqus/Standard 2021 HF7 and 2022 GA.</t>
+          <t>Nonlinear static FEA model of CT-derived femur (DigitalFemur-42) with Ti-6Al-4V stem, surface-to-surface frictional contact (µ = 0.30), 50 µm proximal press-fit interference, and bilinear plastic material for stem; run on Abaqus/Standard 2021 HF7 and 2022 GA with HyperMesh 2020 meshing and Python post-processing.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2037,13 +2097,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>DIC Stereocamera Micromotion Measurements — Sawbones 3403 Rig</t>
+          <t>DIC Micromotion Validation Dataset — Sawbones Rig</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Digital image correlation measurements (7 µm/pixel) of proximal interface micromotion at 8 markers under 2 kN axial plus abductor cable loading on a synthetic femur (Sawbones 3403) used for model validation.</t>
+          <t>Digital image correlation (DIC) stereocamera measurements (7 µm/pixel) of surface micromotion at 8 proximal interface markers on a Sawbones 3403 synthetic femur with Rev F stem under 2 kN axial plus abductor cable loading; used as comparator for FEA validation (Slide 9).</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2057,23 +2117,35 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Bergmann Hip Contact Force Dataset</t>
+          <t>Bergmann Hip Contact Load Dataset</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Literature hip contact force and direction data (Bergmann et al.) downsampled to static peak values to define joint reaction load boundary conditions.</t>
+          <t>Literature-derived hip contact force vectors (Bergmann dataset) downsampled to static peak values used to define joint reaction loads (3.0 kN, 20° anterior, 10° medial) and abductor force (1.2×BW) in the FEA boundary conditions.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="24" t="n"/>
-      <c r="B7" s="24" t="n"/>
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Latin Hypercube Sensitivity Sample — N=25 Completed Runs</t>
+        </is>
+      </c>
       <c r="C7" s="24" t="n"/>
-      <c r="D7" s="33" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Partially completed Latin hypercube sampling study (25 of 100 planned runs) on Medium mesh varying E_cortical, E_cancellous, µ, interference, and abductor force ±15%; results used to estimate 95% uncertainty interval on peak micromotion.</t>
+        </is>
+      </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n"/>
     </row>
@@ -2213,7 +2285,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>DIC vs FEA Micromotion Comparison — Heel-Strike and Single-Leg Stance</t>
+          <t>Mesh Convergence Study</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2228,39 +2300,39 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>RMS micromotion over 8 proximal interface markers compared between Abaqus/Standard FEA predictions and DIC stereo-camera measurements on Sawbones 3403 synthetic femur under two load cases. Headline claim: FEA within 7% of mean DIC across both cases. Detailed results show FEA 38.6 µm vs DIC 45.5 µm (−15%) at heel-strike; FEA 26.2 µm vs DIC 28.4 µm (−7.7%) at single-leg stance.</t>
+          <t>Three-level mesh refinement study (Coarse ~480k, Medium ~1.15M, Fine ~2.9M C3D10 elements) assessing convergence of peak micromotion and stem peak von Mises stress under heel-strike loading. Richardson extrapolation performed to estimate GCI.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>DIC stereocamera measurements on synthetic femur bench test</t>
+          <t>Analytical convergence criterion of &lt;3% change between successive mesh levels; GCI target not explicitly stated</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
-        <is>
-          <t>Quantitative result if applicable</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>Richardson extrapolation (p = 1.92 fit); Grid Convergence Index reported</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>−15% (heel-strike); −7.7% (single-leg stance)</t>
+          <t>Medium→Fine micromotion change: 8.1% (not &lt;3% as claimed); GCI reported as 1.8% in slides but independently computed as 6.8% from same data; stem stress changes: 732→789→846 MPa (coarse to fine)</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study — Peak Micromotion and Stem Stress</t>
+          <t>FEA vs DIC Micromotion Comparison</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2271,27 +2343,23 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Three mesh densities evaluated (Coarse ~480k, Medium ~1.15M, Fine ~2.9M elements). Peak micromotion: 44.1 µm (Coarse), 40.7 µm (Medium), 37.4 µm (Fine). Medium→Fine change is 8.1% (claimed as &lt;3% in Methods). Stem peak stress increases monotonically: 732, 789, 846 MPa. GCI reported as 1.8% in slide notes but notebook calculation yields 6.8% with same data and p=1.92 fit.</t>
+          <t>Comparison of FEA-predicted RMS micromotion (8 proximal interface markers) against DIC stereocamera measurements on Sawbones 3403 synthetic femur with Rev F stem under matched loading conditions (heel-strike and single-leg stance).</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / Grid Convergence Index</t>
+          <t>DIC experimental measurements; headline criterion of FEA within 7% of mean DIC</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="41" t="inlineStr">
-        <is>
-          <t>Richardson extrapolation / GCI (p=1.92 fit)</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="n"/>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>GCI 6.8% (notebook); 8.1% Medium-to-Fine micromotion change</t>
+          <t>Heel-strike: FEA 38.6 µm vs DIC 45.5 µm (−15% error); Single-leg stance: FEA 26.2 µm vs DIC 28.4 µm (−7.7% error); headline summary states "within 7%" which is contradicted by the heel-strike result</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2303,7 +2371,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Contact Pressure Footprint Qualitative Check</t>
+          <t>Latin Hypercube Sensitivity / UQ Study</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2314,21 +2382,29 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>FEA contact pressure footprint compared qualitatively to ink-transfer from bench press-fit tests. General proximal shape reported as consistent; however, FEA predicts peak slip medially (30–45 µm) while DIC shows peak slip laterally (25–35 µm), indicating a spatial discrepancy in slip hotspot location.</t>
+          <t>Partial LHS (25 of 100 planned runs) varying five input parameters (E_cortical, E_cancellous, µ, interference fit, abductor force) ±15% on Medium mesh to estimate uncertainty interval on peak micromotion. Four deterministic corner checks also performed.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Ink-transfer bench press-fit and DIC slip distribution</t>
+          <t>Planned N=100 LHS protocol; reported 95% interval target of ±12%</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="n"/>
-      <c r="H5" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>Latin hypercube sampling; bootstrap 95% confidence interval; coefficient of variation</t>
+        </is>
+      </c>
+      <c r="H5" s="41" t="inlineStr">
+        <is>
+          <t>Reported 95% interval ±12%; actual 25-run filtered set shows CV=9.6%, min/max excursions −18%/+21% vs baseline, bootstrap 95% half-width 14–16%; model-form variant (proximal tie vs full friction) shifts mean −19% and was excluded from UQ</t>
+        </is>
+      </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
           <t>Inconclusive</t>
@@ -2338,7 +2414,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Sensitivity / UQ Latin Hypercube Sampling</t>
+          <t>Contact Pressure Footprint Qualitative Check</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2349,27 +2425,23 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Planned N=100 LHS varying E_cortical, E_cancellous, friction coefficient, interference fit, and abductor force ±15%. Executed: N=28, 25 completed (3 diverged at high μ). Reported 95% interval ±12% about mean; filtered 25-run set shows CV=9.6%, min/max excursion −18%/+21%, bootstrap 95% half-width 14–16%. Model-form variant (proximal tie constraint) shifts mean micromotion −19% and was not included in the UQ envelope.</t>
+          <t>Qualitative comparison of FEA contact pressure footprint against ink-transfer patterns from bench press-fit of Rev F stem into synthetic femur. Slip hotspot locations compared between FEA (medial–proximal 30–45 µm) and bench DIC (lateral 25–35 µm).</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Planned protocol targets</t>
+          <t>Ink-transfer bench test and DIC slip hotspot locations</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>Latin hypercube sampling, bootstrap confidence interval</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Bootstrap 95% half-width 14–16%; excursion range −18%/+21%</t>
+          <t>General shape consistent proximally; hotspot location discrepancy — FEA medial–proximal vs experiment lateral</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2379,14 +2451,43 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="24" t="n"/>
-      <c r="B7" s="24" t="n"/>
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Vendor Benchmark Code Verification</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
       <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="25" t="n"/>
-      <c r="F7" s="33" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Abaqus/Standard 2021 HF7 installation tested against vendor-supplied benchmarks: linear elasticity, Hertz contact, and cantilever reference cases.</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>Analytical reference solutions provided by vendor</t>
+        </is>
+      </c>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="G7" s="33" t="n"/>
-      <c r="H7" s="33" t="n"/>
+      <c r="H7" s="41" t="inlineStr">
+        <is>
+          <t>Maximum error 0.6% across three benchmark cases</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="24" t="n"/>
@@ -2603,12 +2704,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Solver has documented vendor benchmarks; custom subroutines have unit tests; single solver version used consistently.</t>
+          <t>Commercial solver with documented installation qualification; version control on production runs; consistent solver version across study</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Vendor benchmarks for linear elasticity, Hertz contact, and cantilever problems passed at &lt;0.6% error for Abaqus 2021 HF7 install. However, the custom USDFLD field subroutine (used to grade porous layer stiffness) has no documented unit test. Additionally, 13 of 44 production runs were executed on Abaqus 2022 GA due to a license outage, with no side-by-side confirmation that results are equivalent across versions. These gaps reduce confidence in software QA.</t>
+          <t>Abaqus/Standard is a well-established commercial solver with vendor verification documentation. Installation benchmarks (linear elasticity, Hertz contact, cantilever) passed at max 0.6% error. Input decks and scripts are archived in Vault PDM (rev tags r3–r7) with MLFlow parameter tracking. However, 13 of 44 production runs were executed on a different solver version (2022 GA vs 2021 HF7) due to license outage, with no side-by-side confirmation of equivalence. A custom USDFLD field subroutine for porous layer stiffness grading has no documented unit test. Three runs are missing post-processing artifacts. The mixed-version execution and untested custom subroutine represent notable gaps in SQA for this study.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2636,12 +2737,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Code correctness demonstrated via analytical solution comparison or benchmark problems for the relevant physics (contact, nonlinear geometry).</t>
+          <t>Code verified against analytical solutions relevant to the physics of interest, including contact and nonlinear geometry</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Vendor benchmarks cover linear elasticity and Hertz contact, which are partially relevant. However, there is no explicit benchmark for the nonlinear frictional contact problem with large-displacement geometry (NLGEOM) as applied here, and the USDFLD subroutine has no dedicated numerical verification test. The benchmark suite is commercially standard but not specifically tailored to the governing equations of this COU.</t>
+          <t>Vendor benchmarks (linear elasticity, Hertz contact, cantilever) passed at max 0.6% error for the 2021 HF7 installation. These cover some relevant physics (contact, elasticity). However, no verification is documented for the nonlinear geometry (NLGEOM) regime, the bilinear plastic material model, or the USDFLD custom subroutine used to grade porous coating stiffness. No method of manufactured solutions or independent benchmark problems specific to press-fit contact mechanics were performed. Coverage is partial relative to the physics encoded in the model.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2662,19 +2763,19 @@
         </is>
       </c>
       <c r="C7" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with &lt;3% change between refinement levels for key QoI; GCI computed consistently and reported correctly.</t>
+          <t>Mesh convergence demonstrated with &lt;3% change between successive refinement levels for the primary QoI; GCI computed and consistent with claimed value</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three mesh levels were run (Coarse, Medium, Fine). The Medium→Fine peak micromotion change is 8.1%, contradicting the Methods claim of &lt;3%. The reported GCI of 1.8% is inconsistent with the notebook-computed value of 6.8% using the same data (p=1.92). Stem peak stress is not converged (monotonically increasing: 732→789→846 MPa). Production sampling runs used the Medium mesh. Ninety-eight elements have aspect ratio &gt;5 near the calcar. These inconsistencies indicate discretization error is not adequately bounded.</t>
+          <t>A three-level mesh refinement study was performed (Coarse 480k, Medium 1.15M, Fine 2.9M C3D10 elements). However, the Medium→Fine change in peak micromotion is 8.1%, not the 3% claimed in the Methods section. The reported GCI of 1.8% is inconsistent with the value of 6.8% computed from the same datasets using the same p-fit. Stem peak stress increases monotonically (732→789→846 MPa) without convergence. Ninety-eight elements with aspect ratio &gt;5 were retained near the calcar. Production sampling runs used the Medium mesh while Fine was reserved for headline plots only. These inconsistencies prevent confident bounding of discretization error.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2695,19 +2796,19 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Iterative convergence monitored and documented; consistent solver settings applied across all production runs.</t>
+          <t>Iterative solver convergence monitored; residual targets met; contact stabilization settings documented and justified</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Full Newton with line search is used; default contact stabilization (0.0002) applied in some runs. A critical inconsistency exists: NLGEOM is stated as active, but RunSet_12 notes deactivate geometric stiffness for speed ("Small strain OK"), creating non-like-for-like comparisons. One stability run set penalty stiffness to kn=1.0e8 N/mm, reducing predicted slip by ~22% vs auto setting — an effect not discussed in the main text. No residual convergence plots or iteration count records are cited.</t>
+          <t>Abaqus/Standard full Newton with line search was used. Contact stabilization factor 0.0002 was applied in some runs. One stability run used an explicit penalty stiffness (kn = 1.0e8 N/mm) that reduced predicted slip by ~22% vs auto, an undiscussed sensitivity. A preprocessing note on RunSet_12 deactivates geometric stiffness ("Small strain OK") inconsistently with the stated NLGEOM-on setting. Solver convergence monitoring is implied by the use of standard Abaqus settings, but no explicit residual targets or convergence history documentation is provided. Three runs diverged at high µ in the LHS study. Evidence is basic and has notable inconsistencies.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2735,12 +2836,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review confirms boundary conditions, contact settings, and material assignments are correctly implemented; no contradictions between stated and applied settings.</t>
+          <t>Independent review of model setup, boundary conditions, contact definitions, and post-processing; consistent application of settings across all production runs</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Multiple setup contradictions are documented: (1) contact stated as full friction but validation case uses proximal-third tied/distal frictional; (2) NLGEOM stated on but deactivated in RunSet_12; (3) distal constraint varies between encastre and elastic foundation springs without systematic documentation. Internal peer review was conducted by Dr. C. Len, who authored the contact sensitivity section and recused from final sign-off — limiting the independence of the review. Three runs are missing post-processing artifacts.</t>
+          <t>An internal read-across review was performed by Dr. C. Len; however, he authored the contact sensitivity section and recused from final sign-off per QA note, yet his name appears on the approval slide — creating an independence concern. Multiple inconsistencies in model setup were identified in the evidence: (1) full-friction contact stated in Methods but proximal third is tied in the validation case; (2) NLGEOM stated as on but deactivated in RunSet_12; (3) distal constraint varies between encastre and elastic foundation springs across runs without systematic documentation; (4) mixed solver versions without confirmation of equivalence. These use errors are documented as open issues but not resolved.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2768,12 +2869,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations and constitutive model choices are justified; known limitations are documented; model-form sensitivity is quantified.</t>
+          <t>Governing equations and constitutive models justified for the physics regime; known limitations documented; sensitivity to model-form choices quantified</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Linear elastic and bilinear plastic material models are both used for the stem across production runs without consistent selection criteria, making stress comparisons non-like-for-like. The orthotropic bone property set (RunSet_07) was trialed but abandoned due to meshing pipeline limits rather than physical justification. The interference fit ±20 µm tolerance is not modeled. Proximal tie vs full friction is a major model-form variant that shifts micromotion mean by −19% and was excluded from UQ. Limitations are documented in Slides 12 and 14, which is positive, but model-form uncertainty is not fully quantified.</t>
+          <t>The choice of Abaqus/Standard static general with surface-to-surface finite-sliding contact is physically motivated for press-fit micromotion analysis. Isotropic linear elastic bone properties and bilinear plastic Ti-6Al-4V are standard approaches. Known limitations are partially documented (Slide 12): absolute micromotion dependence on contact penalty, plasticity inconsistency across runs, distal constraint variant effects. However, the orthotropic bone model trialed in RunSet_07 was not carried forward due to meshing pipeline limits rather than physical justification. The proximal tie constraint vs full friction model-form choice shifts predicted micromotion by −19% and is excluded from the UQ ensemble, representing an unquantified model-form uncertainty. Liner and acetabular effects are absent and not assessed.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2801,12 +2902,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties and boundary conditions are sourced from measurements or well-characterized literature with uncertainty ranges; input uncertainty is propagated.</t>
+          <t>Material properties traceable to testing or well-characterized literature sources; boundary conditions from measurements; geometric inputs from CMM/QA; input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Cortical bone modulus sourced from Reilly/Carter literature (range 14–18 GPa; 15.5 GPa selected). Cancellous modulus similarly literature-derived (0.3–0.6 GPa; 0.42 GPa used). Interference fit set at nominal 50 µm proximal; ±20 µm QA tolerance not modeled. Hip contact forces from Bergmann dataset, static peaks only. Friction coefficient μ=0.30 from literature but adjusted 0.22→0.34 during insertion force calibration. LHS UQ varied key inputs but with only 25 completed runs and excluding model-form variants. Input uncertainty characterization is partial.</t>
+          <t>Cortical bone modulus (15.5 GPa) and cancellous modulus (420 MPa) are sourced from published literature (Reilly, Carter) with ranges documented (cortical 14–18 GPa, cancellous 0.3–0.6 GPa). Hip contact loads are from the Bergmann dataset. Geometry is CT-derived (DigitalFemur-42). However, the ±20 µm interference fit tolerance identified by QA was not modeled. Friction coefficient µ = 0.30 is from literature but was adjusted (0.22–0.34) to match insertion force, and this calibrated value was also used in the independent validation comparison — conflating calibration and validation data. Load application uses only static peaks from the Bergmann dataset with no dynamic or cyclic loading. Input uncertainty was partially explored through the incomplete LHS but not fully propagated.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2827,19 +2928,19 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Sufficient test specimens with characterization; production-representative or well-characterized surrogate samples.</t>
+          <t>Adequate number of test specimens; production-representative samples; statistical characterization of sample variability</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>A single synthetic femur (Sawbones 3403) was used for DIC validation. No specimen-to-specimen variability is characterized. Sawbones is a standard surrogate but is not production bone; its properties relative to the CT-derived DigitalFemur-42 used in FEA are not reconciled. No sample size justification is provided. A single specimen provides no statistical characterization of variability.</t>
+          <t>Validation used a single Sawbones 3403 synthetic femur with the Rev F stem (Slide 9). Only one specimen is referenced; no replicate tests or statistical characterization of sample variability are documented. Sawbones synthetic femurs are commercially standardized and accepted in orthopaedic biomechanics research as a repeatable surrogate, which partially offsets the single-specimen limitation. No information is provided on stem specimen traceability or whether it is production-representative. The single specimen limits the statistical basis for validation inference.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2867,12 +2968,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation with documented measurement uncertainty; controlled test conditions; test protocol documented to a recognized standard.</t>
+          <t>Calibrated instruments; controlled and documented test environment; measurement uncertainty quantified; test protocol following recognized standards</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>DIC stereocameras at 7 µm/pixel resolution are used, which is appropriate for the measurement scale. Loading is 2 kN axial plus abductor cable; potting at distal 45 mm. However, test load (2 kN) differs from simulation load case (3.0 kN heel-strike), creating a condition mismatch. No instrument calibration records, environmental controls, or formal test standard (ASTM/ISO) are cited. Measurement uncertainty of the DIC system is not reported.</t>
+          <t>DIC stereocameras at 7 µm/pixel resolution were used for micromotion measurement (Slide 9). Potting at distal 45 mm is documented. Loading applied via 2 kN axial plus abductor cable. However, measurement uncertainty is not quantified beyond the stated pixel resolution. No instrument calibration records or traceability to ASTM/ISO standards are cited. The test conditions differ from the FEA load case (2 kN validation test vs 3.0 kN FEA load case), which is an unresolved gap. Environmental controls are not documented. The same operator and rig used for friction calibration performed the DIC comparison two days later, raising concerns about experimental independence.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2900,12 +3001,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model boundary conditions demonstrably match experimental test conditions; all significant differences are identified and their effect on QoI is quantified.</t>
+          <t>FEA boundary conditions matched to experimental conditions; any differences between test and model inputs documented and their effect on QoI quantified</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Several significant mismatches exist between FEA inputs and validation test conditions: (1) validation test load is 2 kN vs simulation heel-strike of 3.0 kN; (2) friction coefficient μ was tuned using the same rig/operator that subsequently ran the DIC comparison, compromising independence; (3) contact treatment differs between production runs and validation case (tied proximal third vs full friction); (4) distal constraint (encastre vs elastic foundation) varies. These mismatches are acknowledged in Slides 13–14 but are not quantitatively reconciled.</t>
+          <t>The FEA validation run uses the Medium mesh with the proximal third tied (not full friction), while the production design runs use full friction — a 19% difference in predicted micromotion. The FEA production load case is 3.0 kN joint reaction while the validation test used 2 kN axial; no explicit load-matched validation run is documented. The friction coefficient used in the validation FEA was calibrated from the same rig's insertion force data, not set independently. The ±20 µm interference tolerance is not modeled. Distal constraint boundary conditions differ between runs. These discrepancies between test and model inputs are identified as open issues but are not quantitatively reconciled, making input parameter equivalency poorly established.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -2926,19 +3027,19 @@
         </is>
       </c>
       <c r="C15" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative comparison of FEA to experimental data at multiple points with uncertainty bands; spatial distribution of errors assessed; metrics consistent across reporting.</t>
+          <t>Quantitative comparison of FEA predictions to experimental measurements; uncertainty bands on both model and experiment; multiple comparison points; statistical validation metrics</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>RMS micromotion over 8 markers is compared for two load cases. Single-leg stance error is −7.7% (acceptable); heel-strike error is −15% (exceeds typical thresholds). The headline "within 7%" claim is inconsistent with the detailed per-load-case data. FEA predicts peak slip medially while DIC shows it laterally — a spatial distribution mismatch not captured by RMS metric alone. No experimental uncertainty bounds are reported. Validation was not conducted with independent data (same rig and operator used for μ calibration and DIC comparison).</t>
+          <t>RMS micromotion over 8 markers is compared between FEA and DIC for two load cases. Heel-strike: FEA 38.6 µm vs DIC 45.5 µm (−15% error). Single-leg stance: FEA 26.2 µm vs DIC 28.4 µm (−7.7%). The headline summary claims "within 7%" which misrepresents the heel-strike result. No experimental uncertainty bands are reported. No statistical validation metric (e.g., TOST, U-value) is applied. Slip hotspot locations show a spatial discrepancy (FEA medial–proximal vs DIC lateral). Comparison is limited to two load cases and one specimen. The absolute error in the higher-load case (15%) approaches the safety margin required for the 40 µm threshold decision. Quantitative comparison exists but has significant gaps and inconsistencies.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -2966,12 +3067,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoI (peak interface micromotion) is directly linked to the clinical/regulatory concern (osseointegration threshold) and is measurable both computationally and experimentally.</t>
+          <t>QoI (peak interface micromotion) directly addresses the safety and performance concern; measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Peak relative micromotion at the proximal medial–lateral interface is the primary QoI and is directly relevant to the 40 µm osseointegration threshold for cementless implant primary stability. This metric is measurable by both FEA (nodal relative displacement at interface) and DIC (surface marker displacement). Secondary QoIs (stem von Mises stress, contact pressure) are also clinically relevant. The QoI choice is well-motivated and consistently applied.</t>
+          <t>Peak relative micromotion at the proximal bone–implant interface is the established biomechanical surrogate for osseointegration risk in cementless stems, with the 40 µm threshold grounded in the published literature and clinical practice. The primary QoI is the same quantity measured experimentally (DIC) and predicted computationally (FEA nodal relative displacement). Secondary QoIs (stem von Mises stress, contact pressure distribution) are also clinically and structurally relevant. The QoI is well-chosen and directly linked to the decision context.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -2992,19 +3093,19 @@
         </is>
       </c>
       <c r="C17" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation test geometry, loading, material, and contact conditions closely match the intended COU; gaps between validation and COU are identified and bounded.</t>
+          <t>Validation conditions (geometry, loading, material, scale) match the intended clinical and mechanical use envelope; gaps between validation and COU are documented and bounded</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation used Sawbones 3403 (surrogate, not CT-derived femur), load magnitude of 2 kN (vs 3.0 kN COU), a single load case, and the same operator who tuned μ. The COU requires absolute acceptance against 40 µm for Rev F under both heel-strike and single-leg stance with a &gt;20% safety margin, but validation conditions do not fully replicate this envelope. Torsional stumble and dynamic cases are excluded from both COU and validation scope, which is consistent. Gaps between validation conditions and COU are acknowledged in Slides 12–14 but are not quantitatively bounded, limiting applicability assessment.</t>
+          <t>Validation used the actual Rev F stem in a Sawbones 3403 synthetic femur, which is relevant geometry. The loading direction and constraint configuration partially match the COU. However, several gaps limit relevance: (1) validation load is 2 kN vs COU load of 3.0 kN — higher loads are not validated; (2) torsional stumble and dynamic oscillations are excluded from both validation and COU scope, which is acceptable but noted; (3) the proximal tie constraint used in validation is not consistent with the full-friction production model; (4) only one bone geometry (DigitalFemur-42) is used, with no assessment of intersubject variability; (5) Sawbones foam does not fully replicate in vivo bone heterogeneity. The validation activities cover the general regime of interest but leave meaningful gaps at the upper end of the load envelope and in model-form consistency.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3093,7 +3194,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The model is not accepted for its stated COU of absolute pass/fail determination against the 40 µm micromotion threshold. Multiple critical deficiencies preclude acceptance: (1) mesh convergence is not demonstrated — Medium→Fine change is 8.1% for the primary QoI with a GCI of 6.8%, and the Methods section contains a contradicted claim of &lt;3%; (2) inconsistent contact treatment (full friction vs proximal tie) and solver settings (NLGEOM on/off) across production runs make results non-comparable; (3) validation is compromised by lack of dataset independence (same operator tuned μ and ran DIC comparison), load magnitude mismatch (2 kN validation vs 3.0 kN COU), and a 15% error in the higher-load heel-strike case; (4) UQ is incomplete — only 25 of planned 100 LHS runs completed, model-form variant (proximal tie) producing −19% shift in micromotion is excluded from the uncertainty envelope, and bootstrap 95% half-width reaches 14–16%; (5) multiple method contradictions are unresolved. The model may be used in a comparative design-ranking role (Rev D vs Rev F) under consistent assumptions, consistent with the Slide 15 recommendation. Absolute acceptance against the 40 µm criterion should be deferred until: mesh convergence is confirmed at &lt;3% for micromotion, contact treatment is standardized, an independent DIC dataset is acquired, the full N=100 LHS is executed including model-form variants, and solver version is locked with cross-version verification.</t>
+          <t>The model is not accepted for its stated purpose of absolute acceptance decision-making against the 40 µm micromotion threshold. Multiple credibility factors fall below the required level for MRL 3: (1) Mesh convergence fails the &lt;3% criterion (8.1% change Medium→Fine) and the GCI is internally inconsistent (1.8% reported vs 6.8% computed); (2) Validation shows up to 15% absolute error in the higher-load heel-strike case, directly relevant to the threshold decision; (3) Model setup contains unresolved inconsistencies — contact treatment (tie vs full friction, 19% effect), solver version (2021 vs 2022, unconfirmed equivalence), NLGEOM activation, and distal constraint strategy vary across runs without systematic justification; (4) The validation dataset is not independent — the same operator and rig used for friction calibration conducted the DIC comparison, and the calibrated µ value was used in the validation FEA; (5) The UQ study is incomplete (25 of 100 planned LHS runs) and excludes the largest identified model-form sensitivity (contact treatment). Per the study's own Slide 14 recommendation and the gate review takeaways (Slide 15), the model is suitable only for comparative design ranking under consistent assumptions. Acceptance for absolute pass/fail against the 40 µm criterion is withheld pending: resolution of contact treatment inconsistency and re-running of validation with consistent settings; locking to a single solver version with cross-version confirmation; completion of mesh convergence to &lt;3% with consistent p-fit; acquisition of a truly independent DIC dataset; and completion of the planned N=100 LHS including contact penalty strategy as a model-form factor.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
